--- a/data/trans_camb/P34A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,9; -19,51</t>
+          <t>-27,87; -19,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,45</t>
+          <t>-7,42; 1,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,26</t>
+          <t>-3,07; 7,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,67; -11,7</t>
+          <t>-19,6; -12,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 8,69</t>
+          <t>0,41; 8,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,64</t>
+          <t>4,88; 12,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,53; -16,23</t>
+          <t>-21,92; -16,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,52</t>
+          <t>-1,82; 4,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,29</t>
+          <t>2,72; 9,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,08; -40,96</t>
+          <t>-54,3; -41,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 5,1</t>
+          <t>-14,65; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 15,06</t>
+          <t>-5,84; 14,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,43; -23,03</t>
+          <t>-36,74; -23,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 17,33</t>
+          <t>0,7; 16,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 25,31</t>
+          <t>8,95; 24,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -32,89</t>
+          <t>-42,32; -32,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 9,04</t>
+          <t>-3,47; 8,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 18,78</t>
+          <t>5,18; 18,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -14,38</t>
+          <t>-20,94; -14,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -5,62</t>
+          <t>-11,74; -5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,07; -7,45</t>
+          <t>-20,79; -7,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,65; -10,01</t>
+          <t>-16,75; -9,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -0,01</t>
+          <t>-6,92; 0,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -4,18</t>
+          <t>-19,16; -3,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -13,08</t>
+          <t>-17,74; -12,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -3,79</t>
+          <t>-8,6; -3,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -7,16</t>
+          <t>-16,89; -6,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,34; -37,17</t>
+          <t>-49,65; -37,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,66; -14,41</t>
+          <t>-27,97; -13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,36; -18,85</t>
+          <t>-51,58; -18,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,95; -23,94</t>
+          <t>-37,09; -23,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -0,12</t>
+          <t>-15,29; 0,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,81; -9,8</t>
+          <t>-42,95; -9,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -32,29</t>
+          <t>-41,32; -32,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -9,3</t>
+          <t>-19,88; -9,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,6; -17,17</t>
+          <t>-40,35; -15,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -7,81</t>
+          <t>-18,71; -8,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 0,97</t>
+          <t>-9,81; 1,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,97</t>
+          <t>-9,05; 2,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,91; -14,83</t>
+          <t>-26,87; -14,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,76; -4,65</t>
+          <t>-16,29; -4,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,61; -7,62</t>
+          <t>-17,78; -7,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,46; -12,33</t>
+          <t>-20,52; -12,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -2,38</t>
+          <t>-10,99; -2,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -3,6</t>
+          <t>-11,38; -3,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,84; -32,0</t>
+          <t>-62,68; -34,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 3,94</t>
+          <t>-32,83; 7,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 7,49</t>
+          <t>-29,58; 8,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,56; -40,94</t>
+          <t>-63,86; -41,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,23; -12,84</t>
+          <t>-39,09; -12,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,79; -21,68</t>
+          <t>-42,23; -20,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,94; -40,09</t>
+          <t>-58,83; -40,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,47; -8,16</t>
+          <t>-31,24; -8,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,15; -12,41</t>
+          <t>-32,99; -11,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,13; -16,43</t>
+          <t>-20,84; -16,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -4,81</t>
+          <t>-9,52; -4,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -6,93</t>
+          <t>-17,23; -6,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -12,72</t>
+          <t>-17,42; -12,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -1,0</t>
+          <t>-5,85; -1,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -4,43</t>
+          <t>-13,96; -4,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,59; -15,15</t>
+          <t>-18,52; -15,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -3,57</t>
+          <t>-6,81; -3,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -6,41</t>
+          <t>-13,93; -6,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,52; -40,66</t>
+          <t>-49,26; -40,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -11,98</t>
+          <t>-22,63; -11,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -17,26</t>
+          <t>-41,72; -16,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -28,47</t>
+          <t>-37,0; -28,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -2,24</t>
+          <t>-12,28; -2,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -9,83</t>
+          <t>-30,46; -9,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -35,45</t>
+          <t>-41,9; -35,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,53; -8,43</t>
+          <t>-15,39; -8,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,12; -14,9</t>
+          <t>-31,51; -14,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P34A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,87; -19,94</t>
+          <t>-28,38; -19,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 1,93</t>
+          <t>-7,78; 2,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,08</t>
+          <t>-2,76; 6,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -12,21</t>
+          <t>-19,7; -11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 8,47</t>
+          <t>-0,44; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,43</t>
+          <t>4,82; 12,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,92; -16,16</t>
+          <t>-22,43; -16,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,45</t>
+          <t>-1,88; 4,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,27</t>
+          <t>2,81; 8,77</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,3; -41,71</t>
+          <t>-54,59; -40,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 3,94</t>
+          <t>-14,9; 4,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 14,84</t>
+          <t>-5,4; 14,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -23,88</t>
+          <t>-36,27; -23,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 16,79</t>
+          <t>-0,81; 16,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 24,66</t>
+          <t>8,91; 24,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -32,76</t>
+          <t>-42,39; -33,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 8,98</t>
+          <t>-3,6; 8,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 18,47</t>
+          <t>5,17; 17,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,17</t>
+          <t>-8,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,6</t>
+          <t>-5,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,87</t>
+          <t>-7,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -14,6</t>
+          <t>-20,59; -14,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -5,22</t>
+          <t>-11,65; -5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,79; -7,35</t>
+          <t>-11,78; -5,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -9,53</t>
+          <t>-16,62; -9,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,02</t>
+          <t>-6,89; -0,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -3,98</t>
+          <t>-9,15; -2,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -12,98</t>
+          <t>-17,91; -13,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -3,84</t>
+          <t>-8,32; -3,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -6,34</t>
+          <t>-9,7; -4,75</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-30,03%</t>
+          <t>-21,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,11%</t>
+          <t>-13,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-25,92%</t>
+          <t>-17,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,65; -37,43</t>
+          <t>-48,76; -37,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,97; -13,77</t>
+          <t>-27,52; -13,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,58; -18,68</t>
+          <t>-28,11; -13,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; -23,52</t>
+          <t>-36,51; -23,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 0,03</t>
+          <t>-15,25; -1,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,95; -9,34</t>
+          <t>-20,06; -6,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,32; -32,13</t>
+          <t>-41,63; -32,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,88; -9,56</t>
+          <t>-19,38; -9,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -15,21</t>
+          <t>-22,48; -11,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,73</t>
+          <t>-12,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,6</t>
+          <t>-7,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,71; -8,52</t>
+          <t>-18,55; -8,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 1,97</t>
+          <t>-9,15; 1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 2,03</t>
+          <t>-9,1; 1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -14,58</t>
+          <t>-26,43; -14,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -4,21</t>
+          <t>-16,49; -4,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -7,34</t>
+          <t>-17,23; -6,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,52; -12,83</t>
+          <t>-20,35; -12,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -2,86</t>
+          <t>-11,08; -2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -3,6</t>
+          <t>-10,76; -3,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,91%</t>
+          <t>-12,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-31,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,47%</t>
+          <t>-22,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,68; -34,18</t>
+          <t>-63,14; -33,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 7,97</t>
+          <t>-31,1; 5,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 8,62</t>
+          <t>-29,85; 7,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -41,73</t>
+          <t>-63,67; -41,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,09; -12,16</t>
+          <t>-39,19; -13,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -20,49</t>
+          <t>-41,27; -19,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,83; -40,49</t>
+          <t>-59,2; -41,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -8,73</t>
+          <t>-31,61; -8,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -11,89</t>
+          <t>-31,43; -10,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,24</t>
+          <t>-7,7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-5,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,13</t>
+          <t>-6,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -16,4</t>
+          <t>-20,84; -16,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -4,76</t>
+          <t>-9,69; -4,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -6,85</t>
+          <t>-10,18; -5,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -12,99</t>
+          <t>-17,58; -12,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -1,23</t>
+          <t>-5,78; -0,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,96; -4,22</t>
+          <t>-7,93; -3,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -15,23</t>
+          <t>-18,57; -15,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -3,54</t>
+          <t>-7,13; -3,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -6,43</t>
+          <t>-8,25; -4,94</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-24,93%</t>
+          <t>-18,74%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,71%</t>
+          <t>-12,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,93%</t>
+          <t>-15,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,26; -40,89</t>
+          <t>-49,5; -40,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -11,95</t>
+          <t>-23,01; -12,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,72; -16,86</t>
+          <t>-24,11; -12,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,0; -28,73</t>
+          <t>-37,28; -28,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -2,73</t>
+          <t>-12,2; -2,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,46; -9,34</t>
+          <t>-16,68; -7,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,9; -35,77</t>
+          <t>-41,88; -35,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -8,35</t>
+          <t>-16,03; -8,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -14,77</t>
+          <t>-18,52; -11,5</t>
         </is>
       </c>
     </row>
